--- a/Группа на заливку.xlsx
+++ b/Группа на заливку.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/roman/Documents/Codex/DD-dev/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F8D05FB-B6E5-6446-8D0D-A84780E5DD49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA410CA-B211-E847-B943-7E3C78483D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19660" activeTab="2" xr2:uid="{0EF5F8DC-ED25-A043-9E19-73CC956363BE}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19660" activeTab="1" xr2:uid="{0EF5F8DC-ED25-A043-9E19-73CC956363BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Продукты на заливку" sheetId="6" r:id="rId1"/>
@@ -17229,7 +17229,7 @@
         <v>229</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>80</v>
@@ -17526,7 +17526,7 @@
         <v>234</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>308</v>
@@ -17823,7 +17823,7 @@
         <v>239</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>84</v>
@@ -18119,8 +18119,8 @@
       <c r="A56" s="19">
         <v>13</v>
       </c>
-      <c r="B56" s="19" t="s">
-        <v>79</v>
+      <c r="B56" s="7" t="s">
+        <v>142</v>
       </c>
       <c r="C56" s="19" t="s">
         <v>86</v>
@@ -18238,8 +18238,8 @@
       <c r="A57" s="19">
         <v>18</v>
       </c>
-      <c r="B57" s="19" t="s">
-        <v>79</v>
+      <c r="B57" s="7" t="s">
+        <v>142</v>
       </c>
       <c r="C57" s="19" t="s">
         <v>86</v>
@@ -18357,8 +18357,8 @@
       <c r="A58" s="19">
         <v>23</v>
       </c>
-      <c r="B58" s="19" t="s">
-        <v>79</v>
+      <c r="B58" s="7" t="s">
+        <v>142</v>
       </c>
       <c r="C58" s="19" t="s">
         <v>90</v>
@@ -18476,8 +18476,8 @@
       <c r="A59" s="19">
         <v>28</v>
       </c>
-      <c r="B59" s="19" t="s">
-        <v>79</v>
+      <c r="B59" s="7" t="s">
+        <v>142</v>
       </c>
       <c r="C59" s="19" t="s">
         <v>91</v>
@@ -18595,8 +18595,8 @@
       <c r="A60" s="19">
         <v>33</v>
       </c>
-      <c r="B60" s="19" t="s">
-        <v>79</v>
+      <c r="B60" s="7" t="s">
+        <v>142</v>
       </c>
       <c r="C60" s="19" t="s">
         <v>84</v>
@@ -18714,8 +18714,8 @@
       <c r="A61" s="19">
         <v>38</v>
       </c>
-      <c r="B61" s="19" t="s">
-        <v>79</v>
+      <c r="B61" s="7" t="s">
+        <v>142</v>
       </c>
       <c r="C61" s="19" t="s">
         <v>93</v>
@@ -18833,8 +18833,8 @@
       <c r="A62" s="19">
         <v>43</v>
       </c>
-      <c r="B62" s="19" t="s">
-        <v>79</v>
+      <c r="B62" s="7" t="s">
+        <v>142</v>
       </c>
       <c r="C62" s="19" t="s">
         <v>82</v>
@@ -30688,7 +30688,7 @@
       <c r="D1">
         <v>17</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F1" t="s">
@@ -30741,7 +30741,7 @@
       <c r="D2">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F2" t="s">
@@ -30794,7 +30794,7 @@
       <c r="D3">
         <v>17</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F3" t="s">
@@ -30847,7 +30847,7 @@
       <c r="D4">
         <v>17</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F4" t="s">
@@ -30900,7 +30900,7 @@
       <c r="D5">
         <v>17</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F5" t="s">
@@ -30953,7 +30953,7 @@
       <c r="D6">
         <v>17</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F6" t="s">
@@ -31006,7 +31006,7 @@
       <c r="D7">
         <v>17</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F7" t="s">
@@ -31059,7 +31059,7 @@
       <c r="D8">
         <v>17</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F8" t="s">
@@ -31112,7 +31112,7 @@
       <c r="D9">
         <v>17</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F9" t="s">
@@ -31165,7 +31165,7 @@
       <c r="D10">
         <v>17</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F10" t="s">
@@ -31218,7 +31218,7 @@
       <c r="D11">
         <v>17</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F11" t="s">
@@ -31271,7 +31271,7 @@
       <c r="D12">
         <v>17</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F12" t="s">
@@ -31324,7 +31324,7 @@
       <c r="D13">
         <v>17</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F13" t="s">
@@ -31377,7 +31377,7 @@
       <c r="D14">
         <v>17</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F14" t="s">
@@ -31430,7 +31430,7 @@
       <c r="D15">
         <v>17</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F15" t="s">
@@ -31483,7 +31483,7 @@
       <c r="D16">
         <v>17</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F16" t="s">
@@ -31536,7 +31536,7 @@
       <c r="D17">
         <v>17</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F17" t="s">
@@ -31589,7 +31589,7 @@
       <c r="D18">
         <v>17</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F18" t="s">
@@ -31642,7 +31642,7 @@
       <c r="D19">
         <v>17</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F19" t="s">
@@ -31695,7 +31695,7 @@
       <c r="D20">
         <v>17</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F20" t="s">
@@ -31748,7 +31748,7 @@
       <c r="D21">
         <v>17</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F21" t="s">
@@ -31801,7 +31801,7 @@
       <c r="D22">
         <v>17</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F22" t="s">
@@ -31854,7 +31854,7 @@
       <c r="D23">
         <v>17</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F23" t="s">
@@ -31907,7 +31907,7 @@
       <c r="D24">
         <v>17</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F24" t="s">
@@ -31960,7 +31960,7 @@
       <c r="D25">
         <v>17</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F25" t="s">
@@ -32013,7 +32013,7 @@
       <c r="D26">
         <v>17</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F26" t="s">
@@ -32066,7 +32066,7 @@
       <c r="D27">
         <v>17</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F27" t="s">
@@ -32119,7 +32119,7 @@
       <c r="D28">
         <v>12</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F28" t="s">
@@ -32172,7 +32172,7 @@
       <c r="D29">
         <v>12</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F29" t="s">
@@ -32225,7 +32225,7 @@
       <c r="D30">
         <v>12</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F30" t="s">
@@ -32278,7 +32278,7 @@
       <c r="D31">
         <v>12</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F31" t="s">
@@ -32331,7 +32331,7 @@
       <c r="D32">
         <v>12</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F32" t="s">
@@ -32384,7 +32384,7 @@
       <c r="D33">
         <v>12</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F33" t="s">
@@ -32437,7 +32437,7 @@
       <c r="D34">
         <v>12</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F34" t="s">
@@ -32490,7 +32490,7 @@
       <c r="D35">
         <v>12</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F35" t="s">
@@ -32543,7 +32543,7 @@
       <c r="D36">
         <v>12</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F36" t="s">
@@ -32596,7 +32596,7 @@
       <c r="D37">
         <v>12</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F37" t="s">
@@ -32649,7 +32649,7 @@
       <c r="D38">
         <v>12</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F38" t="s">
@@ -32702,7 +32702,7 @@
       <c r="D39">
         <v>12</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F39" t="s">
@@ -32755,7 +32755,7 @@
       <c r="D40">
         <v>12</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F40" t="s">
@@ -32808,7 +32808,7 @@
       <c r="D41">
         <v>12</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F41" t="s">
@@ -32861,7 +32861,7 @@
       <c r="D42">
         <v>12</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F42" t="s">
@@ -32914,7 +32914,7 @@
       <c r="D43">
         <v>12</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F43" t="s">
@@ -32967,7 +32967,7 @@
       <c r="D44">
         <v>12</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F44" t="s">
@@ -33020,7 +33020,7 @@
       <c r="D45">
         <v>12</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F45" t="s">
@@ -33073,7 +33073,7 @@
       <c r="D46">
         <v>12</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F46" t="s">
@@ -33126,7 +33126,7 @@
       <c r="D47">
         <v>12</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F47" t="s">
@@ -33179,7 +33179,7 @@
       <c r="D48">
         <v>12</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F48" t="s">
@@ -33232,7 +33232,7 @@
       <c r="D49">
         <v>12</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F49" t="s">
@@ -33285,7 +33285,7 @@
       <c r="D50">
         <v>12</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F50" t="s">
@@ -33338,7 +33338,7 @@
       <c r="D51">
         <v>12</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F51" t="s">
@@ -33391,7 +33391,7 @@
       <c r="D52">
         <v>12</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F52" t="s">
@@ -33444,7 +33444,7 @@
       <c r="D53">
         <v>12</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E53" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F53" t="s">
@@ -33497,7 +33497,7 @@
       <c r="D54">
         <v>12</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E54" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F54" t="s">
@@ -33550,7 +33550,7 @@
       <c r="D55">
         <v>22</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E55" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F55" t="s">
@@ -33603,7 +33603,7 @@
       <c r="D56">
         <v>22</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E56" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F56" t="s">
@@ -33656,7 +33656,7 @@
       <c r="D57">
         <v>22</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E57" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F57" t="s">
@@ -33709,7 +33709,7 @@
       <c r="D58">
         <v>22</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E58" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F58" t="s">
@@ -33762,7 +33762,7 @@
       <c r="D59">
         <v>22</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E59" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F59" t="s">
@@ -33815,7 +33815,7 @@
       <c r="D60">
         <v>22</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E60" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F60" t="s">
@@ -33868,7 +33868,7 @@
       <c r="D61">
         <v>22</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E61" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F61" t="s">
@@ -33921,7 +33921,7 @@
       <c r="D62">
         <v>22</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E62" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F62" t="s">
@@ -33974,7 +33974,7 @@
       <c r="D63">
         <v>22</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E63" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F63" t="s">
@@ -34027,7 +34027,7 @@
       <c r="D64">
         <v>22</v>
       </c>
-      <c r="E64" t="s">
+      <c r="E64" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F64" t="s">
@@ -34080,7 +34080,7 @@
       <c r="D65">
         <v>22</v>
       </c>
-      <c r="E65" t="s">
+      <c r="E65" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F65" t="s">
@@ -34133,7 +34133,7 @@
       <c r="D66">
         <v>22</v>
       </c>
-      <c r="E66" t="s">
+      <c r="E66" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F66" t="s">
@@ -34186,7 +34186,7 @@
       <c r="D67">
         <v>22</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E67" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F67" t="s">
@@ -34239,7 +34239,7 @@
       <c r="D68">
         <v>22</v>
       </c>
-      <c r="E68" t="s">
+      <c r="E68" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F68" t="s">
@@ -34292,7 +34292,7 @@
       <c r="D69">
         <v>22</v>
       </c>
-      <c r="E69" t="s">
+      <c r="E69" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F69" t="s">
@@ -34345,7 +34345,7 @@
       <c r="D70">
         <v>22</v>
       </c>
-      <c r="E70" t="s">
+      <c r="E70" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F70" t="s">
@@ -34398,7 +34398,7 @@
       <c r="D71">
         <v>22</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E71" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F71" t="s">
@@ -34451,7 +34451,7 @@
       <c r="D72">
         <v>22</v>
       </c>
-      <c r="E72" t="s">
+      <c r="E72" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F72" t="s">
@@ -34504,7 +34504,7 @@
       <c r="D73">
         <v>22</v>
       </c>
-      <c r="E73" t="s">
+      <c r="E73" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F73" t="s">
@@ -34557,7 +34557,7 @@
       <c r="D74">
         <v>22</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E74" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F74" t="s">
@@ -34610,7 +34610,7 @@
       <c r="D75">
         <v>22</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E75" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F75" t="s">
@@ -34663,7 +34663,7 @@
       <c r="D76">
         <v>22</v>
       </c>
-      <c r="E76" t="s">
+      <c r="E76" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F76" t="s">
@@ -34716,7 +34716,7 @@
       <c r="D77">
         <v>22</v>
       </c>
-      <c r="E77" t="s">
+      <c r="E77" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F77" t="s">
@@ -34769,7 +34769,7 @@
       <c r="D78">
         <v>22</v>
       </c>
-      <c r="E78" t="s">
+      <c r="E78" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F78" t="s">
@@ -34822,7 +34822,7 @@
       <c r="D79">
         <v>22</v>
       </c>
-      <c r="E79" t="s">
+      <c r="E79" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F79" t="s">
@@ -34875,7 +34875,7 @@
       <c r="D80">
         <v>22</v>
       </c>
-      <c r="E80" t="s">
+      <c r="E80" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F80" t="s">
@@ -34928,7 +34928,7 @@
       <c r="D81">
         <v>22</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E81" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F81" t="s">
@@ -34981,7 +34981,7 @@
       <c r="D82">
         <v>22</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E82" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F82" t="s">
@@ -35034,7 +35034,7 @@
       <c r="D83">
         <v>22</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E83" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F83" t="s">
@@ -35087,7 +35087,7 @@
       <c r="D84">
         <v>22</v>
       </c>
-      <c r="E84" t="s">
+      <c r="E84" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F84" t="s">
@@ -35140,7 +35140,7 @@
       <c r="D85">
         <v>27</v>
       </c>
-      <c r="E85" t="s">
+      <c r="E85" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F85" t="s">
@@ -35193,7 +35193,7 @@
       <c r="D86">
         <v>27</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E86" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F86" t="s">
@@ -35246,7 +35246,7 @@
       <c r="D87">
         <v>27</v>
       </c>
-      <c r="E87" t="s">
+      <c r="E87" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F87" t="s">
@@ -35299,7 +35299,7 @@
       <c r="D88">
         <v>27</v>
       </c>
-      <c r="E88" t="s">
+      <c r="E88" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F88" t="s">
@@ -35352,7 +35352,7 @@
       <c r="D89">
         <v>27</v>
       </c>
-      <c r="E89" t="s">
+      <c r="E89" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F89" t="s">
@@ -35405,7 +35405,7 @@
       <c r="D90">
         <v>27</v>
       </c>
-      <c r="E90" t="s">
+      <c r="E90" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F90" t="s">
@@ -35458,7 +35458,7 @@
       <c r="D91">
         <v>27</v>
       </c>
-      <c r="E91" t="s">
+      <c r="E91" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F91" t="s">
@@ -35511,7 +35511,7 @@
       <c r="D92">
         <v>27</v>
       </c>
-      <c r="E92" t="s">
+      <c r="E92" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F92" t="s">
@@ -35564,7 +35564,7 @@
       <c r="D93">
         <v>27</v>
       </c>
-      <c r="E93" t="s">
+      <c r="E93" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F93" t="s">
@@ -35617,7 +35617,7 @@
       <c r="D94">
         <v>27</v>
       </c>
-      <c r="E94" t="s">
+      <c r="E94" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F94" t="s">
@@ -35670,7 +35670,7 @@
       <c r="D95">
         <v>27</v>
       </c>
-      <c r="E95" t="s">
+      <c r="E95" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F95" t="s">
@@ -35723,7 +35723,7 @@
       <c r="D96">
         <v>27</v>
       </c>
-      <c r="E96" t="s">
+      <c r="E96" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F96" t="s">
@@ -35776,7 +35776,7 @@
       <c r="D97">
         <v>27</v>
       </c>
-      <c r="E97" t="s">
+      <c r="E97" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F97" t="s">
@@ -35829,7 +35829,7 @@
       <c r="D98">
         <v>27</v>
       </c>
-      <c r="E98" t="s">
+      <c r="E98" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F98" t="s">
@@ -35882,7 +35882,7 @@
       <c r="D99">
         <v>27</v>
       </c>
-      <c r="E99" t="s">
+      <c r="E99" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F99" t="s">
@@ -35935,7 +35935,7 @@
       <c r="D100">
         <v>27</v>
       </c>
-      <c r="E100" t="s">
+      <c r="E100" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F100" t="s">
@@ -35988,7 +35988,7 @@
       <c r="D101">
         <v>27</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E101" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F101" t="s">
@@ -36041,7 +36041,7 @@
       <c r="D102">
         <v>27</v>
       </c>
-      <c r="E102" t="s">
+      <c r="E102" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F102" t="s">
@@ -36094,7 +36094,7 @@
       <c r="D103">
         <v>27</v>
       </c>
-      <c r="E103" t="s">
+      <c r="E103" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F103" t="s">
@@ -36147,7 +36147,7 @@
       <c r="D104">
         <v>27</v>
       </c>
-      <c r="E104" t="s">
+      <c r="E104" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F104" t="s">
@@ -36200,7 +36200,7 @@
       <c r="D105">
         <v>27</v>
       </c>
-      <c r="E105" t="s">
+      <c r="E105" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F105" t="s">
@@ -36253,7 +36253,7 @@
       <c r="D106">
         <v>27</v>
       </c>
-      <c r="E106" t="s">
+      <c r="E106" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F106" t="s">
@@ -36306,7 +36306,7 @@
       <c r="D107">
         <v>27</v>
       </c>
-      <c r="E107" t="s">
+      <c r="E107" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F107" t="s">
@@ -36359,7 +36359,7 @@
       <c r="D108">
         <v>27</v>
       </c>
-      <c r="E108" t="s">
+      <c r="E108" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F108" t="s">
@@ -36412,7 +36412,7 @@
       <c r="D109">
         <v>27</v>
       </c>
-      <c r="E109" t="s">
+      <c r="E109" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F109" t="s">
@@ -36465,7 +36465,7 @@
       <c r="D110">
         <v>27</v>
       </c>
-      <c r="E110" t="s">
+      <c r="E110" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F110" t="s">
@@ -36518,7 +36518,7 @@
       <c r="D111">
         <v>27</v>
       </c>
-      <c r="E111" t="s">
+      <c r="E111" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F111" t="s">
@@ -36571,7 +36571,7 @@
       <c r="D112">
         <v>32</v>
       </c>
-      <c r="E112" t="s">
+      <c r="E112" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F112" t="s">
@@ -36624,7 +36624,7 @@
       <c r="D113">
         <v>32</v>
       </c>
-      <c r="E113" t="s">
+      <c r="E113" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F113" t="s">
@@ -36677,7 +36677,7 @@
       <c r="D114">
         <v>32</v>
       </c>
-      <c r="E114" t="s">
+      <c r="E114" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F114" t="s">
@@ -36730,7 +36730,7 @@
       <c r="D115">
         <v>32</v>
       </c>
-      <c r="E115" t="s">
+      <c r="E115" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F115" t="s">
@@ -36783,7 +36783,7 @@
       <c r="D116">
         <v>32</v>
       </c>
-      <c r="E116" t="s">
+      <c r="E116" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F116" t="s">
@@ -36836,7 +36836,7 @@
       <c r="D117">
         <v>32</v>
       </c>
-      <c r="E117" t="s">
+      <c r="E117" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F117" t="s">
@@ -36889,7 +36889,7 @@
       <c r="D118">
         <v>32</v>
       </c>
-      <c r="E118" t="s">
+      <c r="E118" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F118" t="s">
@@ -36942,7 +36942,7 @@
       <c r="D119">
         <v>32</v>
       </c>
-      <c r="E119" t="s">
+      <c r="E119" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F119" t="s">
@@ -36995,7 +36995,7 @@
       <c r="D120">
         <v>32</v>
       </c>
-      <c r="E120" t="s">
+      <c r="E120" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F120" t="s">
@@ -37048,7 +37048,7 @@
       <c r="D121">
         <v>32</v>
       </c>
-      <c r="E121" t="s">
+      <c r="E121" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F121" t="s">
@@ -37101,7 +37101,7 @@
       <c r="D122">
         <v>32</v>
       </c>
-      <c r="E122" t="s">
+      <c r="E122" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F122" t="s">
@@ -37154,7 +37154,7 @@
       <c r="D123">
         <v>32</v>
       </c>
-      <c r="E123" t="s">
+      <c r="E123" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F123" t="s">
@@ -37207,7 +37207,7 @@
       <c r="D124">
         <v>32</v>
       </c>
-      <c r="E124" t="s">
+      <c r="E124" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F124" t="s">
@@ -37260,7 +37260,7 @@
       <c r="D125">
         <v>32</v>
       </c>
-      <c r="E125" t="s">
+      <c r="E125" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F125" t="s">
@@ -37313,7 +37313,7 @@
       <c r="D126">
         <v>32</v>
       </c>
-      <c r="E126" t="s">
+      <c r="E126" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F126" t="s">
@@ -37366,7 +37366,7 @@
       <c r="D127">
         <v>32</v>
       </c>
-      <c r="E127" t="s">
+      <c r="E127" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F127" t="s">
@@ -37419,7 +37419,7 @@
       <c r="D128">
         <v>32</v>
       </c>
-      <c r="E128" t="s">
+      <c r="E128" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F128" t="s">
@@ -37472,7 +37472,7 @@
       <c r="D129">
         <v>32</v>
       </c>
-      <c r="E129" t="s">
+      <c r="E129" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F129" t="s">
@@ -37525,7 +37525,7 @@
       <c r="D130">
         <v>32</v>
       </c>
-      <c r="E130" t="s">
+      <c r="E130" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F130" t="s">
@@ -37578,7 +37578,7 @@
       <c r="D131">
         <v>32</v>
       </c>
-      <c r="E131" t="s">
+      <c r="E131" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F131" t="s">
@@ -37631,7 +37631,7 @@
       <c r="D132">
         <v>32</v>
       </c>
-      <c r="E132" t="s">
+      <c r="E132" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F132" t="s">
@@ -37684,7 +37684,7 @@
       <c r="D133">
         <v>32</v>
       </c>
-      <c r="E133" t="s">
+      <c r="E133" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F133" t="s">
@@ -37737,7 +37737,7 @@
       <c r="D134">
         <v>32</v>
       </c>
-      <c r="E134" t="s">
+      <c r="E134" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F134" t="s">
@@ -37790,7 +37790,7 @@
       <c r="D135">
         <v>32</v>
       </c>
-      <c r="E135" t="s">
+      <c r="E135" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F135" t="s">
@@ -37843,7 +37843,7 @@
       <c r="D136">
         <v>32</v>
       </c>
-      <c r="E136" t="s">
+      <c r="E136" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F136" t="s">
@@ -37896,7 +37896,7 @@
       <c r="D137">
         <v>32</v>
       </c>
-      <c r="E137" t="s">
+      <c r="E137" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F137" t="s">
@@ -37949,7 +37949,7 @@
       <c r="D138">
         <v>32</v>
       </c>
-      <c r="E138" t="s">
+      <c r="E138" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F138" t="s">
@@ -38002,7 +38002,7 @@
       <c r="D139">
         <v>32</v>
       </c>
-      <c r="E139" t="s">
+      <c r="E139" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F139" t="s">
@@ -38055,7 +38055,7 @@
       <c r="D140">
         <v>32</v>
       </c>
-      <c r="E140" t="s">
+      <c r="E140" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F140" t="s">
@@ -38108,7 +38108,7 @@
       <c r="D141">
         <v>32</v>
       </c>
-      <c r="E141" t="s">
+      <c r="E141" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F141" t="s">
@@ -38161,7 +38161,7 @@
       <c r="D142">
         <v>32</v>
       </c>
-      <c r="E142" t="s">
+      <c r="E142" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F142" t="s">
@@ -38214,7 +38214,7 @@
       <c r="D143">
         <v>32</v>
       </c>
-      <c r="E143" t="s">
+      <c r="E143" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F143" t="s">
@@ -38267,7 +38267,7 @@
       <c r="D144">
         <v>37</v>
       </c>
-      <c r="E144" t="s">
+      <c r="E144" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F144" t="s">
@@ -38320,7 +38320,7 @@
       <c r="D145">
         <v>37</v>
       </c>
-      <c r="E145" t="s">
+      <c r="E145" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F145" t="s">
@@ -38373,7 +38373,7 @@
       <c r="D146">
         <v>37</v>
       </c>
-      <c r="E146" t="s">
+      <c r="E146" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F146" t="s">
@@ -38426,7 +38426,7 @@
       <c r="D147">
         <v>37</v>
       </c>
-      <c r="E147" t="s">
+      <c r="E147" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F147" t="s">
@@ -38479,7 +38479,7 @@
       <c r="D148">
         <v>37</v>
       </c>
-      <c r="E148" t="s">
+      <c r="E148" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F148" t="s">
@@ -38532,7 +38532,7 @@
       <c r="D149">
         <v>37</v>
       </c>
-      <c r="E149" t="s">
+      <c r="E149" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F149" t="s">
@@ -38585,7 +38585,7 @@
       <c r="D150">
         <v>37</v>
       </c>
-      <c r="E150" t="s">
+      <c r="E150" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F150" t="s">
@@ -38638,7 +38638,7 @@
       <c r="D151">
         <v>37</v>
       </c>
-      <c r="E151" t="s">
+      <c r="E151" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F151" t="s">
@@ -38691,7 +38691,7 @@
       <c r="D152">
         <v>37</v>
       </c>
-      <c r="E152" t="s">
+      <c r="E152" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F152" t="s">
@@ -38744,7 +38744,7 @@
       <c r="D153">
         <v>37</v>
       </c>
-      <c r="E153" t="s">
+      <c r="E153" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F153" t="s">
@@ -38797,7 +38797,7 @@
       <c r="D154">
         <v>37</v>
       </c>
-      <c r="E154" t="s">
+      <c r="E154" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F154" t="s">
@@ -38850,7 +38850,7 @@
       <c r="D155">
         <v>37</v>
       </c>
-      <c r="E155" t="s">
+      <c r="E155" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F155" t="s">
@@ -38903,7 +38903,7 @@
       <c r="D156">
         <v>37</v>
       </c>
-      <c r="E156" t="s">
+      <c r="E156" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F156" t="s">
@@ -38956,7 +38956,7 @@
       <c r="D157">
         <v>37</v>
       </c>
-      <c r="E157" t="s">
+      <c r="E157" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F157" t="s">
@@ -39009,7 +39009,7 @@
       <c r="D158">
         <v>37</v>
       </c>
-      <c r="E158" t="s">
+      <c r="E158" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F158" t="s">
@@ -39062,7 +39062,7 @@
       <c r="D159">
         <v>37</v>
       </c>
-      <c r="E159" t="s">
+      <c r="E159" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F159" t="s">
@@ -39115,7 +39115,7 @@
       <c r="D160">
         <v>37</v>
       </c>
-      <c r="E160" t="s">
+      <c r="E160" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F160" t="s">
@@ -39168,7 +39168,7 @@
       <c r="D161">
         <v>37</v>
       </c>
-      <c r="E161" t="s">
+      <c r="E161" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F161" t="s">
@@ -39221,7 +39221,7 @@
       <c r="D162">
         <v>37</v>
       </c>
-      <c r="E162" t="s">
+      <c r="E162" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F162" t="s">
@@ -39274,7 +39274,7 @@
       <c r="D163">
         <v>37</v>
       </c>
-      <c r="E163" t="s">
+      <c r="E163" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F163" t="s">
@@ -39327,7 +39327,7 @@
       <c r="D164">
         <v>37</v>
       </c>
-      <c r="E164" t="s">
+      <c r="E164" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F164" t="s">
@@ -39380,7 +39380,7 @@
       <c r="D165">
         <v>37</v>
       </c>
-      <c r="E165" t="s">
+      <c r="E165" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F165" t="s">
@@ -39433,7 +39433,7 @@
       <c r="D166">
         <v>37</v>
       </c>
-      <c r="E166" t="s">
+      <c r="E166" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F166" t="s">
@@ -39486,7 +39486,7 @@
       <c r="D167">
         <v>37</v>
       </c>
-      <c r="E167" t="s">
+      <c r="E167" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F167" t="s">
@@ -39539,7 +39539,7 @@
       <c r="D168">
         <v>37</v>
       </c>
-      <c r="E168" t="s">
+      <c r="E168" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F168" t="s">
@@ -39592,7 +39592,7 @@
       <c r="D169">
         <v>37</v>
       </c>
-      <c r="E169" t="s">
+      <c r="E169" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F169" t="s">
@@ -39645,7 +39645,7 @@
       <c r="D170">
         <v>37</v>
       </c>
-      <c r="E170" t="s">
+      <c r="E170" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F170" t="s">
@@ -39698,7 +39698,7 @@
       <c r="D171">
         <v>37</v>
       </c>
-      <c r="E171" t="s">
+      <c r="E171" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F171" t="s">
@@ -39751,7 +39751,7 @@
       <c r="D172">
         <v>37</v>
       </c>
-      <c r="E172" t="s">
+      <c r="E172" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F172" t="s">
@@ -39804,7 +39804,7 @@
       <c r="D173">
         <v>37</v>
       </c>
-      <c r="E173" t="s">
+      <c r="E173" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F173" t="s">
@@ -39857,7 +39857,7 @@
       <c r="D174">
         <v>37</v>
       </c>
-      <c r="E174" t="s">
+      <c r="E174" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F174" t="s">
@@ -39910,7 +39910,7 @@
       <c r="D175">
         <v>37</v>
       </c>
-      <c r="E175" t="s">
+      <c r="E175" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F175" t="s">
@@ -39963,7 +39963,7 @@
       <c r="D176">
         <v>42</v>
       </c>
-      <c r="E176" t="s">
+      <c r="E176" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F176" t="s">
@@ -40016,7 +40016,7 @@
       <c r="D177">
         <v>42</v>
       </c>
-      <c r="E177" t="s">
+      <c r="E177" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F177" t="s">
@@ -40069,7 +40069,7 @@
       <c r="D178">
         <v>42</v>
       </c>
-      <c r="E178" t="s">
+      <c r="E178" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F178" t="s">
@@ -40122,7 +40122,7 @@
       <c r="D179">
         <v>42</v>
       </c>
-      <c r="E179" t="s">
+      <c r="E179" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F179" t="s">
@@ -40175,7 +40175,7 @@
       <c r="D180">
         <v>42</v>
       </c>
-      <c r="E180" t="s">
+      <c r="E180" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F180" t="s">
@@ -40228,7 +40228,7 @@
       <c r="D181">
         <v>42</v>
       </c>
-      <c r="E181" t="s">
+      <c r="E181" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F181" t="s">
@@ -40281,7 +40281,7 @@
       <c r="D182">
         <v>42</v>
       </c>
-      <c r="E182" t="s">
+      <c r="E182" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F182" t="s">
@@ -40334,7 +40334,7 @@
       <c r="D183">
         <v>42</v>
       </c>
-      <c r="E183" t="s">
+      <c r="E183" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F183" t="s">
@@ -40387,7 +40387,7 @@
       <c r="D184">
         <v>42</v>
       </c>
-      <c r="E184" t="s">
+      <c r="E184" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F184" t="s">
@@ -40440,7 +40440,7 @@
       <c r="D185">
         <v>42</v>
       </c>
-      <c r="E185" t="s">
+      <c r="E185" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F185" t="s">
@@ -40493,7 +40493,7 @@
       <c r="D186">
         <v>42</v>
       </c>
-      <c r="E186" t="s">
+      <c r="E186" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F186" t="s">
@@ -40546,7 +40546,7 @@
       <c r="D187">
         <v>42</v>
       </c>
-      <c r="E187" t="s">
+      <c r="E187" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F187" t="s">
@@ -40599,7 +40599,7 @@
       <c r="D188">
         <v>42</v>
       </c>
-      <c r="E188" t="s">
+      <c r="E188" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F188" t="s">
@@ -40652,7 +40652,7 @@
       <c r="D189">
         <v>42</v>
       </c>
-      <c r="E189" t="s">
+      <c r="E189" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F189" t="s">
@@ -40705,7 +40705,7 @@
       <c r="D190">
         <v>42</v>
       </c>
-      <c r="E190" t="s">
+      <c r="E190" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F190" t="s">
@@ -40758,7 +40758,7 @@
       <c r="D191">
         <v>42</v>
       </c>
-      <c r="E191" t="s">
+      <c r="E191" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F191" t="s">
@@ -40811,7 +40811,7 @@
       <c r="D192">
         <v>42</v>
       </c>
-      <c r="E192" t="s">
+      <c r="E192" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F192" t="s">
@@ -40864,7 +40864,7 @@
       <c r="D193">
         <v>42</v>
       </c>
-      <c r="E193" t="s">
+      <c r="E193" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F193" t="s">
@@ -40917,7 +40917,7 @@
       <c r="D194">
         <v>42</v>
       </c>
-      <c r="E194" t="s">
+      <c r="E194" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F194" t="s">
@@ -40970,7 +40970,7 @@
       <c r="D195">
         <v>42</v>
       </c>
-      <c r="E195" t="s">
+      <c r="E195" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F195" t="s">
@@ -41023,7 +41023,7 @@
       <c r="D196">
         <v>42</v>
       </c>
-      <c r="E196" t="s">
+      <c r="E196" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F196" t="s">
@@ -41076,7 +41076,7 @@
       <c r="D197">
         <v>42</v>
       </c>
-      <c r="E197" t="s">
+      <c r="E197" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F197" t="s">
@@ -41129,7 +41129,7 @@
       <c r="D198">
         <v>42</v>
       </c>
-      <c r="E198" t="s">
+      <c r="E198" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F198" t="s">
@@ -41182,7 +41182,7 @@
       <c r="D199">
         <v>42</v>
       </c>
-      <c r="E199" t="s">
+      <c r="E199" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F199" t="s">
@@ -41235,7 +41235,7 @@
       <c r="D200">
         <v>42</v>
       </c>
-      <c r="E200" t="s">
+      <c r="E200" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F200" t="s">
@@ -41288,7 +41288,7 @@
       <c r="D201">
         <v>42</v>
       </c>
-      <c r="E201" t="s">
+      <c r="E201" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F201" t="s">
@@ -41341,7 +41341,7 @@
       <c r="D202">
         <v>42</v>
       </c>
-      <c r="E202" t="s">
+      <c r="E202" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F202" t="s">
@@ -41394,7 +41394,7 @@
       <c r="D203">
         <v>42</v>
       </c>
-      <c r="E203" t="s">
+      <c r="E203" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F203" t="s">
@@ -41447,7 +41447,7 @@
       <c r="D204">
         <v>42</v>
       </c>
-      <c r="E204" t="s">
+      <c r="E204" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F204" t="s">
@@ -41500,7 +41500,7 @@
       <c r="D205">
         <v>42</v>
       </c>
-      <c r="E205" t="s">
+      <c r="E205" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F205" t="s">
@@ -41553,7 +41553,7 @@
       <c r="D206">
         <v>42</v>
       </c>
-      <c r="E206" t="s">
+      <c r="E206" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F206" t="s">
@@ -41606,7 +41606,7 @@
       <c r="D207">
         <v>17</v>
       </c>
-      <c r="E207" t="s">
+      <c r="E207" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F207" t="s">
@@ -41657,7 +41657,7 @@
       <c r="D208">
         <v>32</v>
       </c>
-      <c r="E208" t="s">
+      <c r="E208" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F208" t="s">
@@ -41707,7 +41707,7 @@
       <c r="D209">
         <v>42</v>
       </c>
-      <c r="E209" t="s">
+      <c r="E209" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F209" t="s">
@@ -41757,7 +41757,7 @@
       <c r="D210">
         <v>37</v>
       </c>
-      <c r="E210" t="s">
+      <c r="E210" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F210" t="s">
@@ -41807,7 +41807,7 @@
       <c r="D211">
         <v>22</v>
       </c>
-      <c r="E211" t="s">
+      <c r="E211" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F211" t="s">
@@ -41857,7 +41857,7 @@
       <c r="D212">
         <v>32</v>
       </c>
-      <c r="E212" t="s">
+      <c r="E212" s="7" t="s">
         <v>142</v>
       </c>
       <c r="F212" t="s">
